--- a/teste.xlsx
+++ b/teste.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024AF76D-9587-4DFA-916B-2F42368EE923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BADF9F8-25E1-478D-B390-0AE1CCC04E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="2415" windowWidth="15375" windowHeight="7785" xr2:uid="{CB8DF74A-12AE-440D-98BF-BE5529FF13D2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CB8DF74A-12AE-440D-98BF-BE5529FF13D2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha3" sheetId="3" r:id="rId1"/>
+    <sheet name="cliente" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha3!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cliente!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>NOME</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">BRRUNA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">roupa </t>
-  </si>
-  <si>
-    <t>SIM</t>
   </si>
 </sst>
 </file>
@@ -145,6 +139,37 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -169,37 +194,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -214,20 +208,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CA4FE74-D418-4E04-A2B6-3DCBE5A84B42}" name="Tabela1" displayName="Tabela1" ref="A1:J2" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CA4FE74-D418-4E04-A2B6-3DCBE5A84B42}" name="Tabela1" displayName="Tabela1" ref="A1:J2" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:J2" xr:uid="{9CA4FE74-D418-4E04-A2B6-3DCBE5A84B42}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A128CF71-A677-4155-B3A3-77820B6402C2}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{62D389A7-C4A9-4AEB-8679-D8EC15078D84}" name="NOME" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{2525B7E7-3403-4ED3-A735-4C4BB518DB85}" name="DDD" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{B5256622-8132-4FCF-B62B-795E149C5DF9}" name="TELEFONE" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{0FDE37E8-4B8D-48E8-BD1D-95CB8C20F520}" name="CELULAR" dataDxfId="7">
-      <calculatedColumnFormula>C2&amp;D2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{8D8B52F4-B7C1-40FA-9A60-096D05D48C80}" name="DATA DE VENCIMENTO" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{A704CB07-137B-4DE7-9D13-D421E88486A7}" name="VALOR" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{85CEE598-28EC-4ADC-849C-EE7B8DA354EE}" name="PRODUTO" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{D7018329-5E57-45CE-B97D-8535EAE9D4BD}" name="STATUS" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{A128CF71-A677-4155-B3A3-77820B6402C2}" name="ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{62D389A7-C4A9-4AEB-8679-D8EC15078D84}" name="NOME" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{2525B7E7-3403-4ED3-A735-4C4BB518DB85}" name="DDD" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{B5256622-8132-4FCF-B62B-795E149C5DF9}" name="TELEFONE" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{0FDE37E8-4B8D-48E8-BD1D-95CB8C20F520}" name="CELULAR" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{8D8B52F4-B7C1-40FA-9A60-096D05D48C80}" name="DATA DE VENCIMENTO" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{A704CB07-137B-4DE7-9D13-D421E88486A7}" name="VALOR" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{85CEE598-28EC-4ADC-849C-EE7B8DA354EE}" name="PRODUTO" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{D7018329-5E57-45CE-B97D-8535EAE9D4BD}" name="STATUS" dataDxfId="1">
       <calculatedColumnFormula>IF(F2="","",IF(J2="Sim","PAGO",IF(F2&lt;TODAY(),"ATRASADO",IF(F2=TODAY(),"VENCE HOJE","NO PRAZO"))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{61E5A83A-0E25-468C-ABC1-79CBCDC63260}" name="PAGO" dataDxfId="0"/>
@@ -594,26 +586,15 @@
       <c r="D2" s="1">
         <v>98753989</v>
       </c>
-      <c r="E2" s="1" t="str">
-        <f>C2&amp;D2</f>
-        <v>3498753989</v>
-      </c>
-      <c r="F2" s="3">
-        <v>46162</v>
-      </c>
-      <c r="G2" s="1">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
       <c r="I2" s="1" t="str">
         <f ca="1">IF(F2="","",IF(J2="Sim","PAGO",IF(F2&lt;TODAY(),"ATRASADO",IF(F2=TODAY(),"VENCE HOJE","NO PRAZO"))))</f>
-        <v>PAGO</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
